--- a/docs/triton-learning/cards/triton-lesson-04-low-memory-dropout-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-04-low-memory-dropout-technical-qa.xlsx
@@ -36,150 +36,152 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inverted dropout 为什么把保留值除以 1-p？</t>
+          <t xml:space="preserve">保留值为什么要除以 1-p？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：为了让每个元素的输出期望保持为原值 x。
-• [T#B#两种结果]：元素以 1-p 的概率输出 x/(1-p)，以 p 的概率输出 0。
+          <t xml:space="preserve">[T#B,!36b59d#结论]：逆 keep probability 缩放抵消随机丢弃，使单元素输出的期望仍为 x。
+• [T#B#结果]：以 1-p 的概率输出 x/(1-p)，以 p 的概率输出0。
 • [T#B#期望]：E(y)=(1-p)×x/(1-p)+p×0=x。
-[T#B,!c47f17#边界]：保持的是随机意义下的期望，不保证每次运行的向量和、均值或范数不变。</t>
+[T#B,!c47f17#边界]：0≤p&lt;1；保持的是随机意义下的期望，不是每次调用都输出原值。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">keep probability × inverse scaling</t>
+          <t xml:space="preserve">保留概率乘缩放系数等于1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-24 Low-Memory Dropout 学习记录</t>
+          <t xml:space="preserve">Lesson 04 · 8/24 学习记录 · inverted scaling</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boundary mask 与 Dropout keep mask 分别回答什么？</t>
+          <t xml:space="preserve">Boundary mask 与 keep mask 有什么区别？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：前者判断 lane 是否对应合法元素，后者判断合法元素是否被保留。
-• [T#B#Boundary]：offset &lt; n_elements，用于保护可能越界的 load/store。
-• [T#B#Keep]：在合法元素中选择输出 0，还是输出经过缩放的输入。
-[T#B,!c47f17#边界]：两者不能互相替代：合法性检查与 Dropout 数学决策是不同职责。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：前者决定能否合法访存，后者决定合法元素的 dropout 输出。
+• [T#B#合法性]：Boundary mask 排除超过 tensor 长度的位置，保护 load/store。
+• [T#B#数学决策]：Keep mask 在合法位置选择清零，或保留并按概率缩放。
+[T#B,!c47f17#边界]：合法元素可能被丢弃；无效位置也不能因“要保留”而允许访存。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">合法 lane / 保留 lane</t>
+          <t xml:space="preserve">访存合法性与随机决策分开</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-24 Low-Memory Dropout 学习记录</t>
+          <t xml:space="preserve">Lesson 04 · 8/24 学习记录 · 两类 mask</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seeded dropout 为什么不能只把 local offsets 传给 tl.rand？</t>
+          <t xml:space="preserve">多 program dropout 为何用 global offsets？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：否则每个 program 会重复同一组随机数和 keep/drop 模式。
-• [T#B#错误映射]：所有 program 都调用 F(seed,0..BLOCK_SIZE-1)，不同 block 形成错误相关性。
-• [T#B#正确映射]：global offset 让元素 i 始终使用 F(seed,i)，成为稳定的随机数身份。
-[T#B,!c47f17#边界]：改变 program 划分不影响身份，前提是每个元素的 global offset 不变。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：相同 seed 配合相同 local offsets 会让不同 program 重复同一随机模式。
+• [T#B#错误]：每个 program 都把0到BLOCK_SIZE-1传入，会让后续 block 重复前一块的 keep/drop 决策。
+• [T#B#修复]：元素 i 使用 F(seed,i)，由 global offset 指定稳定的随机数位置。
+[T#B,!c47f17#边界]：随机数跟随 offset，不会自动跟随被重排的逻辑元素。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">random identity = seed + global offset</t>
+          <t xml:space="preserve">随机身份由 seed 和 global offset 指定</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-24 Low-Memory Dropout 学习记录</t>
+          <t xml:space="preserve">Lesson 04 · 8/24 学习记录 · Triton 3.7.1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">相同 seed 何时才能精确复现一次 seeded dropout？</t>
+          <t xml:space="preserve">相同 seed 怎样保证 dropout 精确复现？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：还必须保持 PRNG 实现、p、输入数值语义以及逻辑元素到 global offset 的映射。
-• [T#B#Mask 复现]：相同 seed、PRNG 与 offset 映射重建相同 keep/drop 决策。
-• [T#B#输出复现]：还需相同 p、输入值与 dtype，以及相同 kernel 数值语义。
-[T#B,!c47f17#边界]：仅改变 BLOCK_SIZE 不一定有影响；重排并连续化会改变逻辑元素的 offset，原决策便不再受保证。不同 seed 也不能保证有限输出一定不同。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先固定随机映射和阈值，再固定输入与数值计算，才能复现最终输出。
+• [T#B#随机数]：保持 seed、PRNG 实现和逻辑元素到 global offset 的映射。
+• [T#B#保留决策]：还须保持 p；同一随机数遇到不同阈值可能改变 keep/drop。
+• [T#B#输出]：保持输入值、dtype 和 kernel 数值语义，才能得到相同数值结果。
+[T#B,!c47f17#边界]：重排会改变 offset 映射，相同 seed 因而不足以保证原决策；不同 seed 也不能保证有限输出一定不同。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">seed 相同不等于元素身份相同</t>
+          <t xml:space="preserve">随机数相同、决策相同、输出相同分三层</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-24 Low-Memory Dropout 学习记录</t>
+          <t xml:space="preserve">Lesson 04 · 8/24 学习记录 · 复现条件</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seeded dropout 把随机状态从 O(N) 降到 O(1)，为何仍不能断言更快？</t>
+          <t xml:space="preserve">随机状态变小，为什么不代表 dropout 更快？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：它减少 mask 的存储和数据移动，但用现场 PRNG 计算换取了这部分收益。
-• [T#B#省下]：不再物化、长期保存并从显存读取完整 keep mask；持久随机状态只需 seed。
-• [T#B#仍存在]：输入和输出流量、逐元素选择与缩放仍然存在，并增加 tl.rand 计算。
-[T#B,!c47f17#边界]：状态复杂度降低不等于设备延迟必然降低；性能取决于内存流量与计算开销的实际权衡。p 是共有算子参数，不是被 seed 替代的随机状态。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：省去了完整 mask 的存储和流量，却增加了现场生成随机数的计算。
+• [T#B#节省]：持久随机状态从 O(N) mask 变为 O(1) seed，避免 mask 的物化、保存和读取。
+• [T#B#代价]：输入/输出访问、逐元素选择与缩放仍存在，还要执行 PRNG。
+[T#B,!c47f17#边界]：状态复杂度不能直接裁决延迟；p 是两种方案共有的参数，不是被 seed 替代的状态。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">memory traffic ↔ PRNG compute</t>
+          <t xml:space="preserve">省 mask 流量，付 PRNG 计算</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-24 Low-Memory Dropout 学习记录</t>
+          <t xml:space="preserve">Lesson 04 · 8/24 学习记录 · 内存取舍</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seeded dropout 的尾部无效 lane，哪些操作要 mask？</t>
+          <t xml:space="preserve">怎样从尾部区间推导安全访存？</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：所有可能越界的 tensor load/store 都要 boundary mask；纯计算的 tl.rand 不需要。
-• [T#B#区间]：tl.arange 的 program 范围是左闭右开的半开区间，不包含右端点。
-• [T#B#守恒]：有效 lane 数加无效 lane 数必须等于 BLOCK_SIZE。
-[T#B,!c47f17#边界]：无效 lane 可以拥有 offset 并计算随机数，但不能据此访问 tensor 内存。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先确定哪些 offset 属于 tensor，再仅允许这些 lane 执行内存访问。
+• [T#B#区间]：n=2057、块长1024时，末块 pid=2 的名义范围为\[2048,3072)。
+• [T#B#计数]：有效范围为\[2048,2057)：有效9、无效1015，总数仍为1024。
+• [T#B#操作]：tl.load 与 tl.store 使用 boundary mask；tl.rand 是纯计算，可计算无效 offset。
+[T#B,!c47f17#边界]：能够生成 offset 或随机数，不代表该位置可以访问 tensor。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">compute safe / memory unsafe</t>
+          <t xml:space="preserve">区间→有效lane→访存保护</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-24 Low-Memory Dropout 学习记录</t>
+          <t xml:space="preserve">Lesson 04 · 8/24 学习记录 · 尾部综合</t>
         </is>
       </c>
     </row>

--- a/docs/triton-learning/cards/triton-lesson-04-low-memory-dropout-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-04-low-memory-dropout-technical-qa.xlsx
@@ -36,15 +36,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">保留值为什么要除以 1-p？</t>
+          <t xml:space="preserve">训练时对一个输入元素 x 做 inverted dropout：以概率 p 丢弃、以概率 1−p 保留。为什么保留分支要输出 x/(1−p)，而不是直接输出 x？</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：逆 keep probability 缩放抵消随机丢弃，使单元素输出的期望仍为 x。
-• [T#B#结果]：以 1-p 的概率输出 x/(1-p)，以 p 的概率输出0。
-• [T#B#期望]：E(y)=(1-p)×x/(1-p)+p×0=x。
-[T#B,!c47f17#边界]：0≤p&lt;1；保持的是随机意义下的期望，不是每次调用都输出原值。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：除以保留概率 1−p，是为了抵消随机清零造成的期望下降，使输出对随机决策取平均后仍等于原输入 x。
+• [T#B#两种输出]：设随机输出为 y：被保留时 y=x/(1−p)，被丢弃时 y=0；两种情况的概率分别为 1−p 和 p。
+[E##\mathbb{E}\lbrack y\rbrack=(1-p)\frac{x}{1-p}+p\cdot0=x]
+• [T#B#不缩放的后果]：如果只随机清零而保留分支仍输出 x，期望就会变为 (1−p)x。例如 x=12、p=0.25 时，不缩放的期望是 9；保留时改输出 16，期望才回到 12。
+[T#B,!c47f17#边界]：要求 0≤p&lt;1。保持的是反复随机采样意义下的单元素期望，不是保证每次调用都输出 x，也不是保证每个有限样本的平均恰好等于 x。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -61,15 +62,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boundary mask 与 keep mask 有什么区别？</t>
+          <t xml:space="preserve">对长度为 n 的向量实现分块 Triton dropout 时，boundary mask（offset&lt;n）与随机生成的 keep mask 分别解决什么问题？</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：前者决定能否合法访存，后者决定合法元素的 dropout 输出。
-• [T#B#合法性]：Boundary mask 排除超过 tensor 长度的位置，保护 load/store。
-• [T#B#数学决策]：Keep mask 在合法位置选择清零，或保留并按概率缩放。
-[T#B,!c47f17#边界]：合法元素可能被丢弃；无效位置也不能因“要保留”而允许访存。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：Boundary mask 判断某个位置能否合法读写 tensor；keep mask 决定合法元素在 dropout 中被清零，还是保留并缩放。它们回答的是两个独立的问题。
+• [T#B#访存边界]：每个 program 生成固定数量的 offset，尾部可能出现 offset≥n。Boundary mask 用于 load/store，防止访问向量范围之外的地址。
+• [T#B#数学分支]：Keep mask 来自随机数与丢弃概率 p 的比较。对合法位置，keep 为真则输出 x/(1−p)，为假则输出 0。
+• [T#B#为何不能混用]：一个合法元素即使被丢弃，也仍有合法输出位置，需要把 0 写回；一个越界位置即使随机结果为“保留”，也不能因此获得访存权限。
+[T#B,!c47f17#边界]：生成一个 offset 或计算该 offset 的随机数，都不等于可以读取对应内存；最终安全性由 boundary mask 保证。</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -86,15 +88,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">多 program dropout 为何用 global offsets？</t>
+          <t xml:space="preserve">多个 Triton program 用同一个 seed 处理同一向量的不同 dropout 分块时，为什么 tl.rand 应接收元素的 global offsets，而不能让每个 program 都传入从 0 开始的 local offsets？</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：相同 seed 配合相同 local offsets 会让不同 program 重复同一随机模式。
-• [T#B#错误]：每个 program 都把0到BLOCK_SIZE-1传入，会让后续 block 重复前一块的 keep/drop 决策。
-• [T#B#修复]：元素 i 使用 F(seed,i)，由 global offset 指定稳定的随机数位置。
-[T#B,!c47f17#边界]：随机数跟随 offset，不会自动跟随被重排的逻辑元素。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：因为给定同一随机数生成实现，seed 与 offset 共同决定随机数；不同 program 若重复传入相同的局部 offset，就会重复生成同一块随机模式。
+• [T#B#坐标定义]：设块长为 B、program 编号为 pid，局部偏移 local 从 0 到 B−1。元素在整条向量中的 global offset 是 pid×B+local。
+• [T#B#错误会怎样出现]：若每个 program 都调用 F(seed,local)，第 0、1、2 块的同一局部位置会使用同一个随机数，进而重复相同的 keep/drop 模式。
+• [T#B#正确随机位置]：应让全局位置 i 的元素调用 F(seed,i)，即使用 tl.rand(seed,global_offsets)，使每块对应自己的随机数位置。
+[T#B,!c47f17#边界]：这里的“身份”是整数 offset，不是元素值或抽象逻辑身份。把 tensor 重排后，若元素对应的 offset 改了，同一 seed 也不保证它沿用原来的决策。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -111,16 +114,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">相同 seed 怎样保证 dropout 精确复现？</t>
+          <t xml:space="preserve">希望在稍后重新计算 seeded dropout，并精确复现同一次前向的输出时，除了保存相同 seed，还必须保持哪些条件？</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先固定随机映射和阈值，再固定输入与数值计算，才能复现最终输出。
-• [T#B#随机数]：保持 seed、PRNG 实现和逻辑元素到 global offset 的映射。
-• [T#B#保留决策]：还须保持 p；同一随机数遇到不同阈值可能改变 keep/drop。
-• [T#B#输出]：保持输入值、dtype 和 kernel 数值语义，才能得到相同数值结果。
-[T#B,!c47f17#边界]：重排会改变 offset 映射，相同 seed 因而不足以保证原决策；不同 seed 也不能保证有限输出一定不同。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：需要分三层检查：先复现每个逻辑元素的随机数，再复现 keep/drop 决策，最后复现数值输出；相同 seed 只覆盖其中一部分条件。
+• [T#B#随机数相同]：保持 seed、伪随机数生成器（PRNG）的实现，以及“逻辑元素到 global offset”的映射。每个元素必须再次调用相同的 F(seed,offset)。
+• [T#B#决策相同]：还要保持丢弃概率 p：即使随机数相同，比较阈值变了，保留与丢弃的判断也可能变化。
+• [T#B#输出相同]：还要保持输入值、dtype 和 kernel 的数值计算语义，因为保留位置输出的是经过缩放的输入，而不是随机数本身。
+[T#B,!c47f17#边界]：重排并重新连续存储可能改变元素的 offset，因此只保存 seed 不够。反过来，不同 seed 在有限样本上也不能保证最终 mask 或输出一定不同。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -137,15 +140,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">随机状态变小，为什么不代表 dropout 更快？</t>
+          <t xml:space="preserve">Low-memory seeded dropout 用 seed 重建随机决策，替代保存长度为 N 的完整 mask。这能减少哪些内存开销，为什么却不能直接断言运行更快？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：省去了完整 mask 的存储和流量，却增加了现场生成随机数的计算。
-• [T#B#节省]：持久随机状态从 O(N) mask 变为 O(1) seed，避免 mask 的物化、保存和读取。
-• [T#B#代价]：输入/输出访问、逐元素选择与缩放仍存在，还要执行 PRNG。
-[T#B,!c47f17#边界]：状态复杂度不能直接裁决延迟；p 是两种方案共有的参数，不是被 seed 替代的状态。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：它用现场生成随机数的计算，换掉完整 mask 的物化、保存和读取；内存状态更少是明确收益，但总延迟还取决于新增计算与其他开销。
+• [T#B#减少的状态]：显式 mask 需要保存随元素数 N 增长的 O(N) 随机决策；在随机映射约定不变时，seeded 方案只需保存 O(1) 的 seed 来重建这些决策。
+• [T#B#仍然存在的工作]：输入和输出 tensor 的访问、每个元素的保留/清零选择，以及 x/(1−p) 的缩放都没有消失。
+• [T#B#新增的代价]：kernel 需要执行伪随机数生成器（PRNG）。省下的 mask 访存与增加的随机数计算谁更重要，取决于目标硬件和实际瓶颈。
+[T#B,!c47f17#边界]：O(N)→O(1) 描述的是持久随机状态，而不是输入/输出的总空间，也不是时间复杂度或实际耗时。丢弃概率 p 是两种方案共有的算子参数。</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -162,16 +166,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">怎样从尾部区间推导安全访存？</t>
+          <t xml:space="preserve">Triton seeded dropout 处理长度 n=2057 的向量，每个 program 生成 1024 个 offset。最后一个 program 应如何确定有效位置，并据此安排 load、随机数计算和 store？</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先确定哪些 offset 属于 tensor，再仅允许这些 lane 执行内存访问。
-• [T#B#区间]：n=2057、块长1024时，末块 pid=2 的名义范围为\[2048,3072)。
-• [T#B#计数]：有效范围为\[2048,2057)：有效9、无效1015，总数仍为1024。
-• [T#B#操作]：tl.load 与 tl.store 使用 boundary mask；tl.rand 是纯计算，可计算无效 offset。
-[T#B,!c47f17#边界]：能够生成 offset 或随机数，不代表该位置可以访问 tensor。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：先用半开区间确定尾块覆盖的全部位置，再用 offset&lt;n 找出有效位置；只有 load/store 需要因此限制内存访问。
+• [T#B#名义覆盖范围]：program 数量为 ceil(2057/1024)=3，编号从 0 开始，因此末块 pid=2。它从 2048 开始生成 1024 个 offset，范围为 \[2048,3072)，不包含 3072。
+• [T#B#有效位置与计数]：与输入范围 \[0,2057) 相交后，有效范围是 \[2048,2057)，共有 9 个位置；其余 1015 个无效，9+1015=1024。
+• [T#B#访存和纯计算]：tl.load 与 tl.store 都使用 boundary mask（offset&lt;2057）。tl.rand 根据 seed 与整数 offset 做计算，不访问该 offset 对应的输入内存，因此可以在无效 offset 上生成随机数。
+[T#B,!c47f17#边界]：能生成某个 offset 或其随机数，不代表 tensor 在该地址有元素。若只保护 store 而没有保护 load，仍可能发生越界读取。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">

--- a/docs/triton-learning/cards/triton-lesson-04-low-memory-dropout-technical-qa.xlsx
+++ b/docs/triton-learning/cards/triton-lesson-04-low-memory-dropout-technical-qa.xlsx
@@ -45,7 +45,8 @@
 • [T#B#两种输出]：设随机输出为 y：被保留时 y=x/(1−p)，被丢弃时 y=0；两种情况的概率分别为 1−p 和 p。
 [E##\mathbb{E}\lbrack y\rbrack=(1-p)\frac{x}{1-p}+p\cdot0=x]
 • [T#B#不缩放的后果]：如果只随机清零而保留分支仍输出 x，期望就会变为 (1−p)x。例如 x=12、p=0.25 时，不缩放的期望是 9；保留时改输出 16，期望才回到 12。
-[T#B,!c47f17#边界]：要求 0≤p&lt;1。保持的是反复随机采样意义下的单元素期望，不是保证每次调用都输出 x，也不是保证每个有限样本的平均恰好等于 x。</t>
+• [T#B#常见误区]：不要把保留时的输出值当成期望：p=0.5 时保留值是 2x，但输出 0 和 2x 各以 0.5 的概率出现，期望仍是 x。
+[T#B,!c47f17#边界]：要求 0≤p&lt;1。保持的是单元素输出的期望，不是每次调用的输出值，也不保证有限样本的平均恰好等于 x。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -69,7 +70,7 @@
         <is>
           <t xml:space="preserve">[T#B,!36b59d#结论]：Boundary mask 判断某个位置能否合法读写 tensor；keep mask 决定合法元素在 dropout 中被清零，还是保留并缩放。它们回答的是两个独立的问题。
 • [T#B#访存边界]：每个 program 生成固定数量的 offset，尾部可能出现 offset≥n。Boundary mask 用于 load/store，防止访问向量范围之外的地址。
-• [T#B#数学分支]：Keep mask 来自随机数与丢弃概率 p 的比较。对合法位置，keep 为真则输出 x/(1−p)，为假则输出 0。
+• [T#B#数学分支]：Keep mask 是 random&gt;p，其中 random 是 tl.rand 为该 offset 生成的 \[0,1) 伪随机数。对合法位置，keep 为真输出 x/(1−p)，为假输出 0。
 • [T#B#为何不能混用]：一个合法元素即使被丢弃，也仍有合法输出位置，需要把 0 写回；一个越界位置即使随机结果为“保留”，也不能因此获得访存权限。
 [T#B,!c47f17#边界]：生成一个 offset 或计算该 offset 的随机数，都不等于可以读取对应内存；最终安全性由 boundary mask 保证。</t>
         </is>
@@ -97,7 +98,7 @@
 • [T#B#坐标定义]：设块长为 B、program 编号为 pid，局部偏移 local 从 0 到 B−1。元素在整条向量中的 global offset 是 pid×B+local。
 • [T#B#错误会怎样出现]：若每个 program 都调用 F(seed,local)，第 0、1、2 块的同一局部位置会使用同一个随机数，进而重复相同的 keep/drop 模式。
 • [T#B#正确随机位置]：应让全局位置 i 的元素调用 F(seed,i)，即使用 tl.rand(seed,global_offsets)，使每块对应自己的随机数位置。
-[T#B,!c47f17#边界]：这里的“身份”是整数 offset，不是元素值或抽象逻辑身份。把 tensor 重排后，若元素对应的 offset 改了，同一 seed 也不保证它沿用原来的决策。</t>
+[T#B,!c47f17#边界]：这里随机数的“身份”是整数 offset，不是元素值或抽象的逻辑元素：同一 seed 下，同一 offset 总得到同一随机数。</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -114,16 +115,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">希望在稍后重新计算 seeded dropout，并精确复现同一次前向的输出时，除了保存相同 seed，还必须保持哪些条件？</t>
+          <t xml:space="preserve">希望稍后重新计算 seeded dropout，并精确复现同一次前向的输出。除了保存相同的 seed，还必须保持哪些条件？请按“随机数相同 → keep 决策相同 → 数值输出相同”三层作答。</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：需要分三层检查：先复现每个逻辑元素的随机数，再复现 keep/drop 决策，最后复现数值输出；相同 seed 只覆盖其中一部分条件。
-• [T#B#随机数相同]：保持 seed、伪随机数生成器（PRNG）的实现，以及“逻辑元素到 global offset”的映射。每个元素必须再次调用相同的 F(seed,offset)。
-• [T#B#决策相同]：还要保持丢弃概率 p：即使随机数相同，比较阈值变了，保留与丢弃的判断也可能变化。
-• [T#B#输出相同]：还要保持输入值、dtype 和 kernel 的数值计算语义，因为保留位置输出的是经过缩放的输入，而不是随机数本身。
-[T#B,!c47f17#边界]：重排并重新连续存储可能改变元素的 offset，因此只保存 seed 不够。反过来，不同 seed 在有限样本上也不能保证最终 mask 或输出一定不同。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：三层各有自己的条件：随机数要保持 PRNG 实现和“逻辑元素 → global offset”映射；决策还要保持丢弃概率 p；数值输出还要保持输入值、dtype 和 kernel 的数值计算语义。
+• [T#B#随机数相同]：每个逻辑元素必须再次调用相同的 F(seed,offset)：除 seed 外，伪随机数生成器（PRNG）的实现和元素到 global offset 的映射都不能变，例如重排后再连续化就会改变映射。
+• [T#B#决策相同]：随机数相同还不够，比较阈值 p 也要相同；p 变了，同一个随机数的保留／丢弃判断也可能变化。
+• [T#B#输出相同]：保留位置输出的是缩放后的输入，而不是随机数本身，所以输入值、dtype 和 kernel 的数值计算语义也要一致。</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -166,26 +166,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Triton seeded dropout 处理长度 n=2057 的向量，每个 program 生成 1024 个 offset。最后一个 program 应如何确定有效位置，并据此安排 load、随机数计算和 store？</t>
+          <t xml:space="preserve">Triton seeded dropout 处理长度 n=2057 的向量，BLOCK_SIZE=1024；最后一个 program（pid=2）的 offsets 是半开区间 \[2048,3072)。这个 program 里的 tl.load、tl.rand 和 tl.store，哪些必须用 offset&lt;n 的 boundary mask？依据是什么？</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">[T#B,!36b59d#结论]：先用半开区间确定尾块覆盖的全部位置，再用 offset&lt;n 找出有效位置；只有 load/store 需要因此限制内存访问。
-• [T#B#名义覆盖范围]：program 数量为 ceil(2057/1024)=3，编号从 0 开始，因此末块 pid=2。它从 2048 开始生成 1024 个 offset，范围为 \[2048,3072)，不包含 3072。
-• [T#B#有效位置与计数]：与输入范围 \[0,2057) 相交后，有效范围是 \[2048,2057)，共有 9 个位置；其余 1015 个无效，9+1015=1024。
-• [T#B#访存和纯计算]：tl.load 与 tl.store 都使用 boundary mask（offset&lt;2057）。tl.rand 根据 seed 与整数 offset 做计算，不访问该 offset 对应的输入内存，因此可以在无效 offset 上生成随机数。
-[T#B,!c47f17#边界]：能生成某个 offset 或其随机数，不代表 tensor 在该地址有元素。若只保护 store 而没有保护 load，仍可能发生越界读取。</t>
+          <t xml:space="preserve">[T#B,!36b59d#结论]：tl.load 和 tl.store 必须用 boundary mask，tl.rand 不需要：只有访问内存的操作才有越界风险。
+• [T#B#有效范围]：末块的 1024 个 offset 中，只有 \[2048,2057) 的 9 个落在输入范围内，其余 1015 个越界。
+• [T#B#访存操作]：tl.load 读输入、tl.store 写输出，都要用 offset&lt;2057 屏蔽越界位置；只保护 store 时，越界的 load 仍会读到向量之外。
+• [T#B#纯计算]：tl.rand 只根据 seed 和整数 offset 计算随机数，不访问该 offset 处的内存，所以在无效 offset 上也可以算；这些位置的结果不会被写回。
+[T#B,!c47f17#边界]：offsets 由 2048 加上 tl.arange(0,1024) 得到，tl.arange 不含右端点，所以末块是 2048…3071，而不是闭区间 \[2048,3072\]。</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">区间→有效lane→访存保护</t>
+          <t xml:space="preserve">访存才要 mask，纯计算不必</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lesson 04 · 8/24 学习记录 · 尾部综合</t>
+          <t xml:space="preserve">Lesson 04 · 8/24 学习记录 · 尾部 mask</t>
         </is>
       </c>
     </row>
